--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0089.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0089.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Golden Anthem</t>
+          <t>Khúc Ca Hoàng Kim</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The One Behind</t>
+          <t>Kẻ Đứng Sau</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Done By Proxy</t>
+          <t>Đã làm xong theo ủy nhiệm</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Những Bài Thơ Của Niềm Kiêu Hãnh</t>
+          <t>Thi Ca Kiêu Hãnh</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Missing Melody</t>
+          <t>Thiếu Melody</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The Order và Hội Thi Sĩ</t>
+          <t>Lệnh Bài và Hội Thi Sĩ</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Những Bài Thơ Khai Mạc</t>
+          <t>Thi Ca Khởi Đầu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Scapegoat</t>
+          <t>Vật tế thần</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The Cursed Poems</t>
+          <t>Những Bài Thơ Bị Nguyền Rủa</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Diverging Paths</t>
+          <t>Những Con Đường Rẽ Nhau</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Thang Đánh Giá Giải Nghĩa</t>
+          <t>Thước Đo Giải Nghĩa</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Echoes of the Anthem</t>
+          <t>Tiếng Vọng Khúc Ca Chiến Thắng</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A Shared Fate</t>
+          <t>Số Phận Chung</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Lắng Nghe "Dư Âm"</t>
+          <t>Hãy lắng nghe "Dư Âm"</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả kết thúc trong Chương I của "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai"</t>
+          <t>Mở khóa tất cả kết thúc trong Chương I của "Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa."</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả kết thúc trong Chương II của "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai"</t>
+          <t>Mở khóa tất cả kết thúc trong Chương II của "Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa."</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả kết thúc trong Chương III của "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai"</t>
+          <t>Mở khóa tất cả kết thúc trong Chương III của "Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa."</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả kết thúc trong Chương IV của "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai"</t>
+          <t>Mở khóa tất cả kết thúc trong Chương IV của "Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa."</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả kết thúc của "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai"</t>
+          <t>Mở khóa tất cả kết thúc của "Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa."</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Chương Cuối: Những Con Đường Rẽ Nhau</t>
+          <t>Chương Cuối: Những Lối Rẽ Khác Nhau</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Replay Story</t>
+          <t>Xem Lại Câu Chuyện</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Bắt Đầu</t>
+          <t>Bắt đầu</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tiếp Tục Từ Lựa Chọn</t>
+          <t>Tiếp tục từ Lựa Chọn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Replay Entire Story</t>
+          <t>Xem Lại Toàn Bộ Câu Chuyện</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Reselect</t>
+          <t>Chọn lại</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Bạn đã thử lựa chọn này trước đây. Tiếp tục?</t>
+          <t>Bạn đã thử tùy chọn này trước đó rồi. Tiếp tục chứ?</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Tiến hành "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai" để mở khóa</t>
+          <t>Tiến hành "Mùa Hè Của Ngươi Sẽ Không Tàn Phai" để mở khóa</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Tiến hành "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai" để mở khóa</t>
+          <t>Tiến hành "Mùa Hè Của Ngươi Sẽ Không Tàn Phai" để mở khóa</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Tiến hành "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Phai" để mở khóa</t>
+          <t>Tiến hành "Mùa Hè Của Ngươi Sẽ Không Tàn Phai" để mở khóa</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Các lựa chọn cần thiết trong Chương IV chưa được hoàn thành</t>
+          <t>Các lựa chọn bắt buộc trong Chương IV chưa được hoàn thành.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Thời Gian Còn Lại</t>
+          <t>Thời gian còn lại</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đến Đường Ban Tặng tại Avinoleum để nhận nhiệm vụ</t>
+          <t>Đến Con Đường Ban Phước ở Avinoleum để nhận nhiệm vụ</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Not Really</t>
+          <t>Không hẳn</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Vui lòng chọn một Resonator</t>
+          <t>Hãy chọn một Resonator đi.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Astral Modulator</t>
+          <t>Bộ Điều Tần Tinh Tú</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Lark Among Clouds</t>
+          <t>Chim Sơn Ca Giữa Mây</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Hero Play Hero</t>
+          <t>Chơi như một Anh Hùng</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Nở Rộ Trong Tuyết</t>
+          <t>Hoa Nở Trong Tuyết</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Crimson Jadeite</t>
+          <t>Ngọc Bích Đỏ Lệ</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Unhindered Perception</t>
+          <t>Nhận Thức Không Giới Hạn</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Leisurely Observer</t>
+          <t>Người Quan Sát Thong Dong</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Flaming Intellect</t>
+          <t>Trí Tuệ Bừng Cháy</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Grand Master</t>
+          <t>Đại Sư</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Market Maker</t>
+          <t>Người tạo lập thị trường</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Lời Thì Thầm Giữa Những Bông Hoa</t>
+          <t>Lời Thì Thầm Giữa Muôn Hoa</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Wooly Warrior</t>
+          <t>Chiến Binh Lông Xù</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Lion Dancer</t>
+          <t>Vũ Công Múa Sư Tử</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Loong Cùng Gió</t>
+          <t>Rồng Cưỡi Gió</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Silent Judge</t>
+          <t>Thẩm Phán Vô Tiếng</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Chrono Thawbringer</t>
+          <t>Kẻ Tan Băng Thời Gian</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>Lửa Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Ánh Nhìn Chân Thực</t>
+          <t>Tầm Nhìn Chân Lý</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Ink Dyed Nature</t>
+          <t>Thiên nhiên nhuốm mực</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Stellar Roamer</t>
+          <t>Kẻ Lang Thang Tinh Tú</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Keen Conservator</t>
+          <t>Người Bảo Vệ Nhạy Bén</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Camellya Rouge</t>
+          <t>Son Camellya</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Sứ Giả Bình Minh</t>
+          <t>Sứ giả Bình Minh</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Overflowing Opal</t>
+          <t>Ngọc Opal Tràn Đầy</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Vũ Công Dưới Ánh Sao</t>
+          <t>Vũ công dưới ánh sao</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>The Merry Fool</t>
+          <t>Kẻ Ngốc Vui Vẻ</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Sứ Giả Ánh Sáng</t>
+          <t>Sứ giả Ánh Sáng</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Thợ Lặn Giấc Mơ</t>
+          <t>Kẻ Lặn Giấc Mơ</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Nghệ Sĩ Đơn Ca Định Mệnh</t>
+          <t>Kẻ Đơn Độc Của Vận Mệnh</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Night Aflame</t>
+          <t>Đêm Cháy Bừng</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Vui lòng thử lại sau</t>
+          <t>Hãy thử lại sau nhé.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Story Node</t>
+          <t>Nút Cốt Truyện</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Replay Story</t>
+          <t>Xem Lại Câu Chuyện</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Vương Quốc Giai Điệu</t>
+          <t>Tổ Tacet Giai Điệu</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Play Ending</t>
+          <t>Phát Kết Thúc</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Endings</t>
+          <t>Các Kết Thúc</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Golden Anthem</t>
+          <t>Khúc Ca Hoàng Kim</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Chapters</t>
+          <t>Các Chương</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Vương Quốc Giai Điệu: Chọn Chương</t>
+          <t>Tổ Tacet Giai Điệu: Chọn Chương</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Phần Thưởng Giới Hạn Thời Gian</t>
+          <t>Các Phần Thưởng Giới Hạn</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Phần thưởng hoàn thành</t>
+          <t>Phần Thưởng Hoàn Thành</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Mùa Hè Của Bạn Sẽ Không Tàn Phai</t>
+          <t>Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Cube Knight</t>
+          <t>Hiệp Sĩ Khối</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Cube Sage</t>
+          <t>Hiền Nhân Khối</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Cube Ranger</t>
+          <t>Kỵ Binh Khối</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Vui lòng hoàn thành màn chơi tiên quyết</t>
+          <t>Hãy hoàn thành màn chơi tiên quyết trước đi.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Attack Frequency</t>
+          <t>Tần số Tấn Công</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Attack Frequency</t>
+          <t>Tần số Tấn Công</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Ability Awakening</t>
+          <t>Thức Tỉnh Kỹ Năng</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Ability Mô-đun</t>
+          <t>Mô-đun Kỹ Năng</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Awakening Mô-đun</t>
+          <t>Mô-đun Thức Tỉnh</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Đăng nhập vào trò chơi trong thời gian sự kiện lần đầu tiên</t>
+          <t>Đăng nhập vào game lần đầu trong sự kiện</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Activity Tasks</t>
+          <t>Nhiệm Vụ Hoạt Động</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Resonator Triệu Tập</t>
+          <t>Triệu Tập Resonator</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Giao hàng Windchimer</t>
+          <t>Giao Hàng Thú Gió</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cubie và xác nhận kết quả của 2 trận đấu "Cubie Derby" trên trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả của 2 trận đấu "Cubie Derby" trên trang sự kiện</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cubie và xác nhận kết quả của 2 trận đấu "Cubie Derby" trên trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 2 trận "Cubie Derby" trên trang sự kiện</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Inspiration</t>
+          <t>Cảm Hứng</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Đêm Đang Ca Hát</t>
+          <t>Đêm Đang Cất Lời</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Dancing Through Fantasies</t>
+          <t>Nhảy Qua Ảo Giác</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Shattered Altar</t>
+          <t>Bàn Thờ Vỡ Nát</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Godkiller</t>
+          <t>Kẻ Sát Thần</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>SỨC MẠNH</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>LỪA ĐẢO</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Biến Đổi</t>
+          <t>Biến hình</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Giai Đoạn Triển Khai</t>
+          <t>Giai đoạn triển khai</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nhận 1.200 Nightmarket Token để mở khóa</t>
+          <t>Thu thập 1.200 Đồng Tiền Chợ Đêm để mở khóa</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Nhận 2.200 Nightmarket Token để mở khóa</t>
+          <t>Thu thập 2.200 Nightmarket Token để mở khóa</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Nhận 1000 Nightmarket Token để mở khóa</t>
+          <t>Thu thập 1.000 Thẻ Chợ Đêm để mở khóa</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tiêu 2000 Nightmarket Token để mở khóa</t>
+          <t>Dùng 2000 Điểm Chợ Đêm để mở khóa</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Unactivated</t>
+          <t>Chưa kích hoạt</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Frame</t>
+          <t>Khung Hình</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Thay thế Mô-đun</t>
+          <t>Mô-đun đã thay thế</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Trang bị Mô-đun</t>
+          <t>Mô-đun đã trang bị</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Gỡ Mô-đun</t>
+          <t>Mô-đun đã gỡ bỏ</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Thử Thách Cá Nhân</t>
+          <t>Thử Thách Solo</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Thử Thách Đồng Đội</t>
+          <t>Thử thách Đồng Đội</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Ending 1</t>
+          <t>Kết Thúc 1</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Ending 2</t>
+          <t>Kết Thúc 2</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ending 3</t>
+          <t>Kết Thúc 3</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Kết thúc Câu chuyện hiện tại</t>
+          <t>Kết Thúc Câu Chuyện Hiện Tại</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Weapon Triệu Tập</t>
+          <t>Triệu Hoán Vũ Khí</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Triệu Tập</t>
+          <t>Triệu Tập Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Đứng sau Zani!</t>
+          <t>Đứng sau Zani đi!</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>I Will Become Fear</t>
+          <t>Ta Sẽ Trở Thành Nỗi Kinh Hoàng</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>The Magistrate's Fortune Stick</t>
+          <t>Quẻ Bói của Thị Trưởng</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Warm Marble</t>
+          <t>Đá Cẩm Thạch Ấm</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Puppy Cookie</t>
+          <t>Bánh Quy Chó Con</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Unknown Matter</t>
+          <t>Vật chất bí ẩn</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Amusement Park Annual Pass</t>
+          <t>Vé Tham Quan Công Viên Hằng Năm</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Orange Slice</t>
+          <t>Múi Cam</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Lollipop</t>
+          <t>Kẹo mút</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Một loại Kẹo nào đó</t>
+          <t>Loại Kẹo Gì Đó</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Spare Suits</t>
+          <t>Trang bị dự phòng</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Đầu Cá, Đuôi Cá, Xương Cá</t>
+          <t>Đầu Cá, Đuôi Cá, Xương Cá I</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cây Gậy bị Gãy</t>
+          <t>Cây Gậy Phép Hỏng</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Bộ Echo hiện tại đã đầy, không thể thêm Echo mới</t>
+          <t>Bộ Echo hiện tại đã đầy, không thể thêm mới.</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Ability Mô-đun</t>
+          <t>Mô-đun Kỹ Năng</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Mô-đun</t>
+          <t>Mô-đun tiêu chuẩn</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Awakening Mô-đun</t>
+          <t>Mô-đun Thức Tỉnh</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Ready Cube One</t>
+          <t>Khối Một sẵn sàng</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Free Cube</t>
+          <t>Khối Lập Phương miễn phí</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Wreck-it Cube</t>
+          <t>Khối Phá Hủy</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Inland Empire</t>
+          <t>Đế quốc Nội lục</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Somnoire Film Critic</t>
+          <t>Nhà Phê Bình Phim Somnoire</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>In: Spectre</t>
+          <t>Vào: Bóng Ma</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CHI PHÍ</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Chọn Echo để thay ra</t>
+          <t>Chọn Echo để thay thế</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Không bắt buộc phải đổi nếu bạn hài lòng với các thẻ hiện tại</t>
+          <t>Không cần đổi nếu cậu thấy vui với những lá bài hiện tại.</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Duel Begins</t>
+          <t>Trận đấu bắt đầu</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Mở Khóa 4 Khối Resonator</t>
+          <t>Mở khóa 4 Khối Resonator</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Mở Khóa 6 Khối Resonator</t>
+          <t>Mở khóa 6 Khối Resonator</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Mở Khóa 9 Khối Resonator</t>
+          <t>Mở khóa 9 Khối Resonator</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Mở Khóa 12 Khối Resonator</t>
+          <t>Mở khóa 12 Khối Resonator</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 10.000 1st Anniversary Coin</t>
+          <t>Thu thập tổng cộng 10.000 Đồng Kỷ Niệm Năm Đầu Tiên</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 20.000 1st Anniversary Coin</t>
+          <t>Thu thập tổng cộng 20.000 Đồng Kỷ Niệm 1 Năm</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 25.000 1st Anniversary Coin</t>
+          <t>Thu thập tổng cộng 25.000 Đồng Kỷ Niệm 1 Năm</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 30.000 1st Anniversary Coin</t>
+          <t>Thu thập tổng cộng 30.000 Đồng xu Kỷ niệm 1 năm</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Hoàn thành Abbowser Castle Cấp 5</t>
+          <t>Hoàn thành Lâu Đài Abbowser Cấp 5</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Hoàn thành Abbowser Castle Cấp 10</t>
+          <t>Hoàn thành Lâu Đài Abbowser Cấp 10</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Hoàn thành Abbowser Castle Cấp 12</t>
+          <t>Hoàn thành Lâu Đài Abbowser Cấp 12</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Hoàn thành Abbowser Castle Cấp 15</t>
+          <t>Hoàn thành Lâu Đài Abbowser Cấp 15</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Hoàn thành Abbowser Castle Cấp 18</t>
+          <t>Hoàn thành Lâu Đài Abbowser Cấp 18</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Hoàn thành Abbowser Castle Cấp 20</t>
+          <t>Hoàn thành Lâu Đài Abbowser Cấp 20</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Tiến độ 20% ở Abbowser Castle Cấp 21</t>
+          <t>Đã đạt 20% tiến độ ở Cung Điện Abbowser Cấp 21</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Tiến độ 40% ở Abbowser Castle Cấp 21</t>
+          <t>Đã đạt 40% tiến độ ở Cung Điện Abbowser Cấp 21</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Tiến độ 60% ở Abbowser Castle Cấp 21</t>
+          <t>Đã đạt 60% tiến độ ở Cung Điện Abbowser Cấp 21</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Tiến độ 80% ở Abbowser Castle Cấp 21</t>
+          <t>Đã đạt 80% tiến độ ở Cung Điện Abbowser Cấp 21</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Havoc Reaper</t>
+          <t>Kẻ Gặt Hỗn Loạn</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>The Vanguard Gale</t>
+          <t>Cơn Gió Tiền Phong</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Not Locked</t>
+          <t>Chưa Khóa</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Glider</t>
+          <t>Dù lượn</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Flight</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Show Trang phục</t>
+          <t>Hiển thị Trang Phục</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Later Storyline Resources</t>
+          <t>Tài nguyên Cốt truyện Sau</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Later Storyline Resources</t>
+          <t>Tài nguyên Cốt truyện Sau</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Tài nguyên để thay đổi ngoại hình của Rover</t>
+          <t>Tài nguyên Thay đổi Ngoại hình của Rover</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tài nguyên để thay đổi ngoại hình của Rover</t>
+          <t>Tài nguyên Thay đổi Ngoại hình của Rover</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>New Deck</t>
+          <t>Bộ Thẻ Mới</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Last Deck</t>
+          <t>Bộ Bài Cuối Cùng</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Deck Incomplete</t>
+          <t>Bộ bài chưa hoàn chỉnh</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Tải xuống tài nguyên còn thiếu để tiếp tục</t>
+          <t>Tải tài nguyên còn thiếu để tiếp tục</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Đến trang tải xuống</t>
+          <t>Tải xuống thôi</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Tiến về phía trước</t>
+          <t>Tiến lên phía trước.</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Downloaded</t>
+          <t>Đã tải xong</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Resources Downloaded</t>
+          <t>Tài Nguyên Đã Tải</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Lượt Đối Phương</t>
+          <t>Lượt của đối thủ</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Lượt của bạn</t>
+          <t>Lượt của cậu</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Dùng Zani để hoàn thành Tầng 1 &amp; Tầng 2 Tháp Nguy Hiểm trong "Tower of Adversity: Hazard Zone"</t>
+          <t>Dùng Zani để vượt qua Tầng 1 &amp; Tầng 2 Tháp Hazard trong "Tower of Adversity: Hazard Zone".</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Dùng Ciaccona để hoàn thành Tầng 1 &amp; Tầng 2 Tháp Nguy Hiểm trong "Tower of Adversity: Hazard Zone"</t>
+          <t>Dùng Ciaccona để vượt qua Tầng 1 &amp; Tầng 2 của Tháp Nguy Hiểm trong "Tower of Adversity: Hazard Zone".</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Mùa Hè Của Bạn Sẽ Không Tàn Phai</t>
+          <t>Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Bộ Thẻ Mặc Định</t>
+          <t>Bộ bài mặc định</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Echo Cốt lõi</t>
+          <t>Tiếng Vọng Cốt Lõi</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Thường Echo</t>
+          <t>Tiếng Vọng Thường</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Echo này đang bị khóa</t>
+          <t>Hồi Âm này đã bị khóa.</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tất cả Cards</t>
+          <t>Tất Cả Thẻ</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Cost 1</t>
+          <t>Chi Phí 1</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Cost 3</t>
+          <t>Chi phí: 3</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Echo Cốt lõi</t>
+          <t>Tiếng Vọng Cốt Lõi</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Fusion</t>
+          <t>Hợp Nhất</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Đang chờ tài nguyên khác trong hàng đợi tải xuống</t>
+          <t>Đang chờ các tài nguyên khác trong hàng tải xuống</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Vui lòng đợi tải xong tài nguyên hiện tại</t>
+          <t>Vui lòng chờ tải xong tài nguyên hiện tại</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Afterstory</t>
+          <t>Hậu Truyện</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Cube, Cubic và Cubie</t>
+          <t>Khối, Khối Lập Phương và Cubie</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Deliver</t>
+          <t>Giao hàng</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Năng lượng không đủ để sử dụng Resonator Tactic</t>
+          <t>Năng lượng không đủ để sử dụng Chiến Thuật Resonator</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Echo không có hiệu ứng Biến Hóa không thể kéo vào khu vực Biến Đổi</t>
+          <t>Echo không có Hiệu Ứng Biến Hóa không thể kéo vào Khu Vực Biến Hóa</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Chi phí 3 Echo chỉ có thể triển khai thông qua Modulation</t>
+          <t>Chi phí 3 Echo chỉ có thể triển khai qua Điều Tần</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>The Ironheart</t>
+          <t>Trái Tim Sắt</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>The Splendent</t>
+          <t>Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>The Lifespring</t>
+          <t>Dòng Suối Sự Sống</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>The Dustbound</t>
+          <t>Vùng Đất Bụi</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>The Nightmare</t>
+          <t>Ác Mộng</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>The Firebrand</t>
+          <t>Ngọn Lửa Đốt Cháy</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Thử thách Vô tận</t>
+          <t>Thử Thách Vô Tận</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>The Ironheart's Trial</t>
+          <t>Thử Thách Trái Tim Sắt</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>The Ironheart's Trial</t>
+          <t>Thử Thách Trái Tim Sắt</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>The Splendent's Trial</t>
+          <t>Thử Thách Của Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>The Splendent's Trial</t>
+          <t>Thử Thách Của Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>The Splendent's Trial</t>
+          <t>Thử Thách Của Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>The Lifespring's Trial</t>
+          <t>Thử Thách Của Dòng Suối Sự Sống</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>The Lifespring's Trial</t>
+          <t>Thử Thách Của Dòng Suối Sự Sống</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>The Lifespring's Trial</t>
+          <t>Thử Thách Của Dòng Suối Sự Sống</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>The Dustbound's Trial</t>
+          <t>Thử Thách Vùng Đất Bụi</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>The Dustbound's Trial</t>
+          <t>Thử Thách Vùng Đất Bụi</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>The Dustbound's Trial</t>
+          <t>Thử Thách Vùng Đất Bụi</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>The Dustbound's Trial</t>
+          <t>Thử Thách Vùng Đất Bụi</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>The Nightmare's Trial</t>
+          <t>Thử Thách Ác Mộng</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>The Nightmare's Trial</t>
+          <t>Thử Thách Ác Mộng</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>The Nightmare's Trial</t>
+          <t>Thử Thách Ác Mộng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>The Nightmare's Trial</t>
+          <t>Thử Thách Ác Mộng</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Apex Challenge</t>
+          <t>Thử Thách Đỉnh Cao</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Apex Challenge</t>
+          <t>Thử Thách Đỉnh Cao</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Apex Challenge</t>
+          <t>Thử Thách Đỉnh Cao</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Apex Challenge</t>
+          <t>Thử Thách Đỉnh Cao</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Mysterious Challenger</t>
+          <t>Đối Thủ Bí Ẩn</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Mysterious Challenger</t>
+          <t>Đối Thủ Bí Ẩn</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mysterious Challenger</t>
+          <t>Đối Thủ Bí Ẩn</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Mysterious Challenger</t>
+          <t>Đối Thủ Bí Ẩn</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Thử thách Vô tận</t>
+          <t>Thử Thách Vô Tận</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Thử thách Vô tận</t>
+          <t>Thử Thách Vô Tận</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Duelist's Challenge</t>
+          <t>Thử Thách của Duelist</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Duelist's Challenge</t>
+          <t>Thử Thách của Duelist</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Duelist's Challenge</t>
+          <t>Thử Thách của Duelist</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Practice Duel</t>
+          <t>Trận đấu tập</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Practice Duel</t>
+          <t>Trận đấu tập</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Practice Duel</t>
+          <t>Trận đấu tập</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Novice Duelist</t>
+          <t>Duel Tân Thủ</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Novice Duelist</t>
+          <t>Duel Tân Thủ</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Novice Duelist</t>
+          <t>Duel Tân Thủ</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Novice Duelist</t>
+          <t>Duel Tân Thủ</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Novice Duelist</t>
+          <t>Duel Tân Thủ</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Apprentice Duelist</t>
+          <t>Duelist Tập Sự</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Apprentice Duelist</t>
+          <t>Duelist Tập Sự</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Apprentice Duelist</t>
+          <t>Duelist Tập Sự</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Apprentice Duelist</t>
+          <t>Duelist Tập Sự</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Trained Duelist</t>
+          <t>Duelist Đã Tôi Luyện</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Trained Duelist</t>
+          <t>Duelist Đã Tôi Luyện</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Trained Duelist</t>
+          <t>Duelist Đã Tôi Luyện</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Trained Duelist</t>
+          <t>Duelist Đã Tôi Luyện</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Skilled Duelist</t>
+          <t>Đấu sĩ tài ba</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Skilled Duelist</t>
+          <t>Đấu sĩ tài ba</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Skilled Duelist</t>
+          <t>Đấu sĩ tài ba</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Skilled Duelist</t>
+          <t>Đấu sĩ tài ba</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Expert Duelist</t>
+          <t>Bậc Thầy Đấu Kiếm</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Expert Duelist</t>
+          <t>Bậc Thầy Đấu Kiếm</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Expert Duelist</t>
+          <t>Bậc Thầy Đấu Kiếm</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Expert Duelist</t>
+          <t>Bậc Thầy Đấu Kiếm</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Master Duelist</t>
+          <t>Bậc Thầy Đấu Thủ</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Master Duelist</t>
+          <t>Bậc Thầy Đấu Thủ</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Master Duelist</t>
+          <t>Bậc Thầy Đấu Thủ</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Master Duelist</t>
+          <t>Bậc Thầy Đấu Thủ</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Apex Duelist</t>
+          <t>Duelist Đỉnh Cao</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Apex Duelist</t>
+          <t>Duelist Đỉnh Cao</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Apex Duelist</t>
+          <t>Duelist Đỉnh Cao</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Apex Duelist</t>
+          <t>Duelist Đỉnh Cao</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Hocus Pocus</t>
+          <t>Ảo thuật biến!</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Nocturnus Knight</t>
+          <t>Hiệp Sĩ Nocturnus</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Abyssal Patricius</t>
+          <t>Quý Tộc Vực Sâu</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Hooscamp Flinger</t>
+          <t>Quái Hooscamp Ném Vật</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Galescourge Stalker</t>
+          <t>Thợ Săn Gale Scourge</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Ảo tưởng Không đường lui</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Chop Chop: Leftless</t>
+          <t>Chop Chop: Không Tay Trái</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Nimbus Wraith</t>
+          <t>Hồn Ma Nimbus</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Diurnus Knight</t>
+          <t>Hiệp Sĩ Diurnus</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Voltscourge Stalker</t>
+          <t>Kẻ Rình Rập Sét Tàn Phá</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Vitreum Dancer</t>
+          <t>Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Questless Knight</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Dwarf Cassowary</t>
+          <t>Đà Điểu Lùn</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Diggy Duggy</t>
+          <t>Đào Đi Đào Đi</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Spearback</t>
+          <t>Lưng Lao</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>The Ironheart's Trial</t>
+          <t>Thử Thách Trái Tim Sắt</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>The Splendent's Trial</t>
+          <t>Thử Thách Của Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Thử Thách Vết Bụi</t>
+          <t>Thử Thách Cát Bụi</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Agrippa the Ironheart</t>
+          <t>Agrippa Trái Tim Sắt</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Người Phụ Nữ Nhút Nhát</t>
+          <t>Người phụ nữ bẽn lẽn</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Phấn Khích</t>
+          <t>Người đàn ông hào hứng</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Liliania the Splendent</t>
+          <t>Liliana Rực Rỡ</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Care-Refusing Patient</t>
+          <t>Bệnh Nhân Từ Chối Điều Trị</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Recovering Patient</t>
+          <t>Bệnh Nhân Đang Hồi Phục</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Marcia the Lifespring</t>
+          <t>Marcia Suối Nguồn Sống</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Grandino Gladiator</t>
+          <t>Đấu sĩ Grandino</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Grandino Agent</t>
+          <t>Đặc vụ Grandino</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Grandino Head</t>
+          <t>Thủ lĩnh Grandino</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Raul the Dustbound</t>
+          <t>Raul Bụi Đời</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Người Phụ Nữ Tức Giận</t>
+          <t>Người phụ nữ nổi giận</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Trưởng Lão Trầm Lặng</t>
+          <t>Trưởng Lão Lặng Lẽ</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Gallus the Nightmare</t>
+          <t>Gallus Ác Mộng</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Cheerful Duelist</t>
+          <t>Duelist Vui Vẻ</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Arrogant Duelist</t>
+          <t>Kẻ Khiêu Chiến Kiêu Ngạo</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Contemplative Duelist</t>
+          <t>Đấu Sĩ Trầm Ngâm</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Furius the Firebrand</t>
+          <t>Furius Ngọn Lửa Bất Khuất</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Mysterious Challenger - Brant</t>
+          <t>Đối Thủ Bí Ẩn - Brant</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Mysterious Challenger - Ciaccona</t>
+          <t>Đối Thủ Bí Ẩn - Ciaccona</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Mysterious Challenger - Lupa</t>
+          <t>Đối Thủ Bí Ẩn - Lupa</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Mysterious Challenger - Calcharo</t>
+          <t>Đối Thủ Bí Ẩn - Calcharo</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Thử Thách Vô Tận - Thường</t>
+          <t>Thử Thách Vô Tận - Bình Thường</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Thử Thách Vô Tận - Khó</t>
+          <t>Thử Thách Vô Tận - Cấp Độ Khó</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Thử Thách của Danvers</t>
+          <t>Thử thách của Danvers</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Thử Thách của Fulvia</t>
+          <t>Thử thách của Fulvia</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Thử Thách của Furius</t>
+          <t>Thử Thách Của Furius</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Thử Thách của Raul</t>
+          <t>Thử Thách Của Raul</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Thử Thách của Liliania</t>
+          <t>Thử Thách Của Liliania</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Thử Thách của Patient</t>
+          <t>Thử Thách Kiên Nhẫn</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Resonant Blessing</t>
+          <t>Phúc Lành Cộng Hưởng</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Woolies' Wonderland</t>
+          <t>Thế Giới Kỳ Diệu của Woolies</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Mandatory Overtime</t>
+          <t>Tăng ca bắt buộc</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Productivity Boost</t>
+          <t>Tăng hiệu suất</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Sinh Tồn Của Kẻ Mạnh Nhất</t>
+          <t>Sự sống sót của kẻ mạnh nhất</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Slow-Burn Satisfaction</t>
+          <t>Thỏa Mãn Chậm Rãi</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Matter Reconstruction</t>
+          <t>Tái Cấu Trúc Vật Chất</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Hệ thống Overload</t>
+          <t>Hệ Thống Quá Tải</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Fatal Flaw</t>
+          <t>Lỗi Lầm Chết Người</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Crystal Tango</t>
+          <t>Điệu Tango Pha Lê</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Đánh Bại Gallus the Nightmare</t>
+          <t>Đánh bại Gallus Ác Mộng</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Đánh Bại Raul the Dustbound</t>
+          <t>Đánh bại Raul the Dustbound.</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đánh Bại Gallus the Nightmare</t>
+          <t>Đánh bại Gallus Ác Mộng</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Đủ Điều Kiện Vào Chung Kết Với Nhà Vô Địch Uy Tín</t>
+          <t>Đủ điều kiện vào trận chung kết tranh danh hiệu Nhà Chinh Phục Uy Tín</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Không có hiệu ứng</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Sự kiện chưa khả dụng hoặc chưa đáp ứng điều kiện mở khóa</t>
+          <t>Sự kiện chưa khả dụng hoặc chưa đáp ứng đủ điều kiện mở khóa</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>I'm On Fire</t>
+          <t>Ta đang bốc cháy đây</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>I'm Down Nhưng Alive</t>
+          <t>Tôi là Down But Alive.</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Crawling Forward</t>
+          <t>Bò Tiến Lên</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Ground Game Expert</t>
+          <t>Chuyên gia Trò chơi Mặt đất</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Repetition Side Steps</t>
+          <t>Bước tránh lặp lại</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Dark Lightning</t>
+          <t>Sấm Chớp Hắc Ám</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>My Name Is Shadow</t>
+          <t>Ta Là Bóng Tối</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Crazy Diamond</t>
+          <t>Kim Cương Điên Cuồng</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Monster Reborn</t>
+          <t>Quái vật hồi sinh</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Armor Up</t>
+          <t>Mặc Áo Giáp</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Armor Pen Resonator</t>
+          <t>Resonator Xuyên Giáp</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Rock Solid</t>
+          <t>Vững Như Đá</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
